--- a/output/pdf_financials_xlsx/BPF.UN.xlsx
+++ b/output/pdf_financials_xlsx/BPF.UN.xlsx
@@ -1446,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>33.78</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>34.204</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
@@ -4950,15 +4950,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.951</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>3.036</v>
@@ -4983,10 +4979,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>12.766</v>
+        <v>1.285</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>12.276</v>
+        <v>1.021</v>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
@@ -20830,7 +20826,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -50869,7 +50865,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>CashEquivalents</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -74104,7 +74100,11 @@
           <t>Royalty expense (note 17)</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BPF.UN.xlsx
+++ b/output/pdf_financials_xlsx/BPF.UN.xlsx
@@ -599,20 +599,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>-1.844</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>-1.808</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-1.217</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-0.04</v>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
@@ -629,11 +639,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>-0.274</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>-0.17</v>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -652,35 +666,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>21.391</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>4.969</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>5.422</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>4.768</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>4.513</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>5.732</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>7.045</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>7.038</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>6.365</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>6.923</v>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
@@ -697,11 +731,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>7.749</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>8.087999999999999</v>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1644,19 +1682,19 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>-1.844</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>-1.808</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>-1.217</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1674,10 +1712,10 @@
         </is>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0</v>
+        <v>-0.274</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="19">
@@ -2786,16 +2824,16 @@
         <v>16.492</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>58.661</v>
+        <v>60.505</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>80.43600000000001</v>
+        <v>82.244</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.29</v>
+        <v>5.507</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>29.543</v>
+        <v>29.576</v>
       </c>
       <c r="M33" s="1" t="inlineStr">
         <is>
@@ -2818,10 +2856,10 @@
         </is>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>43.943</v>
+        <v>44.217</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>56.881</v>
+        <v>57.051</v>
       </c>
     </row>
     <row r="34">
@@ -2926,16 +2964,16 @@
         <v>16.492</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>58.661</v>
+        <v>60.505</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>80.43600000000001</v>
+        <v>82.244</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>7.454</v>
+        <v>8.670999999999999</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>33.28</v>
+        <v>33.313</v>
       </c>
       <c r="M35" s="1" t="inlineStr">
         <is>
@@ -2958,10 +2996,10 @@
         </is>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>43.943</v>
+        <v>44.217</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>56.881</v>
+        <v>57.051</v>
       </c>
     </row>
     <row r="36">
@@ -2998,16 +3036,16 @@
         <v>52.72884228026985</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>144.0134534652493</v>
+        <v>148.5404954214028</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>183.4553540882655</v>
+        <v>187.5789713764397</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>6.049637216550067</v>
+        <v>7.03734965182528</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>72.96485496919603</v>
+        <v>73.03720593716429</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -3030,10 +3068,10 @@
         </is>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>88.75939242142684</v>
+        <v>89.31283832915892</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>109.624761500954</v>
+        <v>109.9523965540502</v>
       </c>
     </row>
     <row r="37">
@@ -3726,10 +3764,10 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2.986</v>
+        <v>0.001</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2.829</v>
+        <v>0.003</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0.453</v>
@@ -3753,12 +3791,10 @@
         <v>3.541</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>3.296</v>
-      </c>
-      <c r="L46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.659</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.886</v>
       </c>
       <c r="M46" s="1" t="inlineStr">
         <is>
@@ -3886,10 +3922,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.986</v>
+        <v>0.001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.829</v>
+        <v>0.003</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.453</v>
@@ -3913,12 +3949,10 @@
         <v>3.541</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.296</v>
-      </c>
-      <c r="L48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.659</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.886</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -4950,11 +4984,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>0.951</v>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E60" s="3" t="n">
         <v>3.036</v>
@@ -4979,10 +5017,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>1.285</v>
+        <v>12.403</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>1.021</v>
+        <v>11.39</v>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
@@ -20626,7 +20664,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -20826,7 +20864,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -50865,7 +50903,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -69331,7 +69369,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -69424,7 +69462,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -80086,7 +80124,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -84502,7 +84540,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -86108,7 +86146,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -87908,7 +87946,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">

--- a/output/pdf_financials_xlsx/BPF.UN.xlsx
+++ b/output/pdf_financials_xlsx/BPF.UN.xlsx
@@ -10604,10 +10604,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>0</v>
+        <v>-1.874</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>0</v>
+        <v>-1.175</v>
       </c>
       <c r="M131" s="3" t="n">
         <v>0</v>
@@ -10796,50 +10796,32 @@
       <c r="I134" s="3" t="n">
         <v>-138.687</v>
       </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>6.003</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -11471,10 +11453,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I144" s="3" t="n">
+        <v>107.264</v>
       </c>
       <c r="J144" s="3" t="n">
         <v>-36.558</v>
@@ -11830,80 +11810,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D150" s="3" t="n">
+        <v>26.185</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>19.062</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>24.908</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>33.151</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>36.858</v>
+      </c>
+      <c r="K150" s="3" t="n">
+        <v>-6.401</v>
+      </c>
+      <c r="L150" s="3" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="M150" s="3" t="n">
+        <v>35.621</v>
+      </c>
+      <c r="N150" s="3" t="n">
+        <v>22.866</v>
+      </c>
+      <c r="O150" s="3" t="n">
+        <v>30.475</v>
+      </c>
+      <c r="P150" s="3" t="n">
+        <v>37.926</v>
+      </c>
+      <c r="Q150" s="3" t="n">
+        <v>38.122</v>
+      </c>
+      <c r="R150" s="3" t="n">
+        <v>39.698</v>
       </c>
     </row>
   </sheetData>
@@ -53541,7 +53491,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -54238,7 +54192,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -56190,7 +56148,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -56984,7 +56946,11 @@
           <t>Acquisition of Fund Units (note 11(d)) (3,456) - (3,456) Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -57582,7 +57548,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -58368,7 +58338,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -59411,7 +59385,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -60298,7 +60276,11 @@
           <t>Deferred income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -61500,7 +61482,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -62310,7 +62296,11 @@
           <t>Purchase of intangible assets, net (note 18)</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -64914,7 +64904,11 @@
           <t>Net cash generated from operating activities 33,151</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -66215,7 +66209,11 @@
           <t>RL Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -66920,7 +66918,11 @@
           <t>NN Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>
@@ -67829,7 +67831,11 @@
           <t>E M Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -76051,7 +76057,11 @@
           <t>Deferred income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
           <t>-</t>
